--- a/data/2026/cjsl/fall/fa-euro-new-york-2014-2015-pre-mls-iii.xlsx
+++ b/data/2026/cjsl/fall/fa-euro-new-york-2014-2015-pre-mls-iii.xlsx
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/fa-euro-new-york-2014-2015-pre-mls-iii.xlsx
+++ b/data/2026/cjsl/fall/fa-euro-new-york-2014-2015-pre-mls-iii.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 - 3</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/fa-euro-new-york-2014-2015-pre-mls-iii.xlsx
+++ b/data/2026/cjsl/fall/fa-euro-new-york-2014-2015-pre-mls-iii.xlsx
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 - 1</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/fa-euro-new-york-2014-2015-pre-mls-iii.xlsx
+++ b/data/2026/cjsl/fall/fa-euro-new-york-2014-2015-pre-mls-iii.xlsx
@@ -329,7 +329,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6 - 8</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
